--- a/DateBase/orders/Dang Nguyen 195_2026-8-22.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-8-22.xlsx
@@ -1078,6 +1078,9 @@
       <c r="G2" t="str">
         <v>01271013410126101065101010101010351515301055510551520303020101010555301010520101012588101010485201015101562105105</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
